--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СОУТ подписанты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СОУТ подписанты'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СОУТ подписанты'!$A$1:$J$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,22 +441,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
+    <row r="1" ht="55" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№ п/п</t>
@@ -508,7 +508,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="55" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="55" customHeight="1">
+    <row r="3" ht="50" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="55" customHeight="1">
+    <row r="4" ht="50" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -624,12 +624,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н) — результаты идентификации заносятся в перечень РМ</t>
+          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, подлежащих СОУТ (утверждаемый комиссией до начала работ)</t>
+          <t>Перечень рабочих мест, подлежащих СОУТ</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест для проведения СОУТ; указание аналогичных рабочих мест</t>
+          <t>Перечень рабочих мест, на которых будет проводиться СОУТ; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="55" customHeight="1">
+    <row r="5" ht="50" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н) — результаты идентификации заносятся в перечень РМ</t>
+          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, подлежащих СОУТ (утверждаемый комиссией до начала работ)</t>
+          <t>Перечень рабочих мест, подлежащих СОУТ</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест для проведения СОУТ; указание аналогичных рабочих мест</t>
+          <t>Перечень рабочих мест, на которых будет проводиться СОУТ; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="55" customHeight="1">
+    <row r="6" ht="50" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -749,7 +749,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="55" customHeight="1">
+    <row r="7" ht="50" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -794,12 +794,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Организация, проводящая СОУТ (уполномоченное лицо)</t>
+          <t>Уполномоченное лицо организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="55" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -824,12 +824,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3 ФЗ-426; приложение № 3 к приказу № 817н (титульный лист); п. 2 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ (титульный лист)</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -854,11 +854,11 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -874,12 +874,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3 ФЗ-426; приложение № 3 к приказу № 817н (титульный лист); п. 2 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ (титульный лист)</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -904,11 +904,11 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -924,12 +924,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 1 ФЗ-426; раздел I приложения № 3 к приказу № 817н; п. 3 Инструкции (приложение № 4) — сведения подписываются руководителем и заверяются печатью (при наличии)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ (раздел I — сведения об организации, проводящей СОУТ)</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -949,16 +949,16 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации (при наличии)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -974,12 +974,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 2 ФЗ-426; раздел II приложения № 3 к приказу № 817н; п. 4 Инструкции (приложение № 4) — раздел II подписывается председателем, членами комиссии и экспертом (экспертами)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ (раздел II — перечень рабочих мест, на которых проводилась СОУТ)</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -994,21 +994,21 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Эксперт организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 2 ФЗ-426; раздел II приложения № 3 к приказу № 817н; п. 4 Инструкции (приложение № 4) — раздел II подписывается председателем, членами комиссии и экспертом (экспертами)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ (раздел II — перечень рабочих мест, на которых проводилась СОУТ)</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1044,21 +1044,21 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Работник, занятый на рабочем месте</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>собственноручная</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1074,32 +1074,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 2 ФЗ-426; раздел II приложения № 3 к приказу № 817н; п. 4 Инструкции (приложение № 4) — раздел II подписывается председателем, членами комиссии и экспертом (экспертами)</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ (раздел II — перечень рабочих мест, на которых проводилась СОУТ)</t>
+          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="55" customHeight="1">
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1124,32 +1124,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="55" customHeight="1">
+    <row r="15" ht="50" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1169,37 +1169,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Письменные замечания и возражения работника относительно результатов СОУТ (при наличии)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Замечания и возражения работника относительно результатов СОУТ на его рабочем месте</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="55" customHeight="1">
+    <row r="16" ht="50" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1224,32 +1224,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Мотивированное особое мнение члена комиссии по СОУТ (при наличии)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Письменное мотивированное особое мнение члена комиссии; при подписании отчета — пометка «особое мнение»</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="55" customHeight="1">
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1269,17 +1269,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 11 ФЗ-426; Порядок подачи декларации и форма (приказ Минтруда № 406н)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1294,21 +1294,21 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Работник, занятый на данном рабочем месте</t>
+          <t>Руководитель юридического лица (работодатель)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>собственноручная или УКЭП</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="55" customHeight="1">
+          <t>Да — место печати (М.П.), заверение печатью (при наличии) (приказ № 406н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 15 ч. 1 п. 4 ФЗ-426; Методика (приложение № 1 к приказу № 817н) — оформление результатов исследований (испытаний) и измерений</t>
+          <t>ст. 11 ФЗ-426; Порядок подачи декларации и форма (приказ Минтруда № 406н)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов</t>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Эксперт / работник испытательной лаборатории (центра) организации, проводящей СОУТ</t>
+          <t>Индивидуальный предприниматель (работодатель)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>собственноручная или УКЭП</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="55" customHeight="1">
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1369,37 +1369,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 5 ФЗ-426; Методика / форма отчета (приказ № 817н)</t>
+          <t>ст. 15 ч. 5.1 ФЗ-426</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Протокол оценки эффективности средств индивидуальной защиты (при проведении такой оценки)</t>
+          <t>Уведомление организации, проводившей СОУТ, об утверждении отчета и направление копии утвержденного отчета</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Сведения об утверждении отчета; копия утвержденного отчета</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Работодатель</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>УКЭП</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1408,858 +1408,8 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="55" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 5 ФЗ-426; Методика / форма отчета (приказ № 817н)</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Протокол оценки эффективности средств индивидуальной защиты (при проведении такой оценки)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по СОУТ (в составе отчета)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="55" customHeight="1">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 5 ФЗ-426; Методика / форма отчета (приказ № 817н)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Протокол оценки эффективности средств индивидуальной защиты (при проведении такой оценки)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ (в составе отчета)</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="55" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; неотъемлемая часть отчета</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="55" customHeight="1">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; неотъемлемая часть отчета</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="55" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н (форма сводной ведомости)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="55" customHeight="1">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н (форма сводной ведомости)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="55" customHeight="1">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н (форма сводной ведомости)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="55" customHeight="1">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="55" customHeight="1">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="55" customHeight="1">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 9 ФЗ-426; п. 6, 10–11 Методики (приложение № 1 к приказу № 817н) — заключение эксперта по результатам идентификации</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Заключение эксперта организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="55" customHeight="1">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Письменные замечания и возражения работника относительно результатов СОУТ (при наличии)</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Замечания и возражения работника относительно результатов СОУТ на его рабочем месте</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Работник</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="55" customHeight="1">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н) — подписание отчета с пометкой «особое мнение»</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Мотивированное особое мнение члена комиссии по СОУТ (при наличии)</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Письменное мотивированное особое мнение; отметка «особое мнение» при подписании отчета</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или НЭП или УКЭП</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="55" customHeight="1">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н (форма и порядок подачи декларации)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>ст. 11 ФЗ-426; приложение № 1 и Порядок подачи к приказу Минтруда № 406н — подпись руководителя / ИП, заверение печатью (при наличии); электронная подача — УКЭП</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Руководитель юридического лица (работодатель)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Да — место печати (М.П.), заверение печатью (при наличии)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="55" customHeight="1">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н (форма и порядок подачи декларации)</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>ст. 11 ФЗ-426; приложение № 1 и Порядок подачи к приказу Минтруда № 406н — подпись руководителя / ИП, заверение печатью (при наличии); электронная подача — УКЭП</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Индивидуальный предприниматель (работодатель)</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Нет (для ИП печать не требуется; подписывается лично)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="55" customHeight="1">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 5.1 ФЗ-426</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Уведомление организации, проводившей СОУТ, об утверждении отчета и направление копии утвержденного отчета</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Сведения об утверждении отчета; копия утвержденного отчета</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Работодатель</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="55" customHeight="1">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>ст. 4 ч. 2 п. 4, ст. 5 ч. 2, ст. 15 ч. 5 ФЗ-426; раздел III формы отчета (приказ № 817н) — ознакомление работников с результатами в Карте</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Лист (запись) ознакомления работников с результатами СОУТ</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена)</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Работник, занятый на рабочем месте</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J36"/>
+  <autoFilter ref="A1:J19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СОУТ подписанты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СОУТ подписанты'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СОУТ подписанты'!$A$1:$J$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,17 +441,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
@@ -508,7 +508,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -539,7 +539,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Состав комиссии (нечётное число); порядок деятельности комиссии; председатель комиссии; представители работодателя (включая специалиста по ОТ); представители выборного органа профсоюза / иного представительного органа работников (при наличии)</t>
+          <t>Состав комиссии (нечётное число); порядок деятельности комиссии; председатель; представители работодателя (включая специалиста по ОТ); представители выборного органа профсоюза / иного представительного органа работников (при наличии)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="50" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -608,7 +608,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="50" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -658,7 +658,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="50" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -708,7 +708,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="50" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -758,7 +758,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="50" customHeight="1">
+    <row r="7" ht="48" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -808,7 +808,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="50" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -824,41 +824,41 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
+          <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н) — результаты идентификации оформляются экспертом; по результатам идентификации оформляется заключение</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Результаты идентификации; при несовпадении наименований факторов с классификатором — фиксация отсутствия на РМ вредных и (или) опасных факторов, предусмотренных классификатором</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Эксперт организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -874,41 +874,41 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н) — решения комиссии оформляются протоколом заседания</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Протокол заседания комиссии по проведению СОУТ (решения комиссии)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Решения комиссии (в т.ч. о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -924,27 +924,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н) — решения комиссии оформляются протоколом заседания</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Протокол заседания комиссии по проведению СОУТ (решения комиссии)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Решения комиссии (в т.ч. о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Руководитель организации, проводящей СОУТ</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -954,11 +954,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -974,27 +974,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Перечень факторов, подлежащих исследованиям (испытаниям) и измерениям, исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемых оборудования, материалов и сырья</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1004,11 +1004,11 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1024,41 +1024,41 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н (форма отчета и инструкция по заполнению)</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Перечень факторов, подлежащих исследованиям (испытаниям) и измерениям, исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемых оборудования, материалов и сырья</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Работник, занятый на рабочем месте</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 6, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>Полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер РМ, должность/профессия/специальность; наименование фактора по классификатору; дата исследований/измерений; сведения о средствах измерений; методики (методы) измерений и реквизиты утвердивших их актов; реквизиты актов о ПДК/ПДУ/нормативах; место измерений (при необходимости — эскиз); нормативные и фактические значения, продолжительность воздействия; заключение по фактическому уровню фактора с итоговым классом (подклассом); ФИО и должности специалистов, проводивших исследования (испытания) и измерения (п. 20 Методики, приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
+    <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
+          <t>Заключение эксперта о возможности использования результатов производственного контроля (при наличии)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной ИЛ (центром) при производственном контроле; прилагается к протоколу</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Эксперт организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="50" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1169,32 +1169,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426</t>
+          <t>ст. 15 ч. 1 п. 5 ФЗ-426; форма отчета / Методика (приказ № 817н)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Письменные замечания и возражения работника относительно результатов СОУТ (при наличии)</t>
+          <t>Протокол оценки эффективности средств индивидуальной защиты (при проведении такой оценки)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Замечания и возражения работника относительно результатов СОУТ на его рабочем месте</t>
+          <t>Не требуется (форма утверждена)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Эксперт организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="50" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Мотивированное особое мнение члена комиссии по СОУТ (при наличии)</t>
+          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Письменное мотивированное особое мнение члена комиссии; при подписании отчета — пометка «особое мнение»</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="50" customHeight="1">
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1269,46 +1269,46 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; Порядок подачи декларации и форма (приказ Минтруда № 406н)</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Руководитель юридического лица (работодатель)</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Да — место печати (М.П.), заверение печатью (при наличии) (приказ № 406н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="50" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; Порядок подачи декларации и форма (приказ Минтруда № 406н)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1344,21 +1344,21 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Индивидуальный предприниматель (работодатель)</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="50" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1369,47 +1369,997 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Отчет о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или НЭП или УКЭП</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Отчет о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Руководитель организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Отчет о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Работник, занятый на данном рабочем месте</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 9 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Заключение эксперта организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 5.1 ФЗ-426</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Письменные замечания и возражения работника относительно результатов СОУТ (при наличии)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Замечания и возражения работника относительно результатов СОУТ на его рабочем месте</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11 Методики — особое мнение к протоколу заседания</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Мотивированное особое мнение члена комиссии по СОУТ (при наличии)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Письменное мотивированное (аргументированное) особое мнение члена комиссии</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Руководитель юридического лица (работодатель)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Да — место печати (М.П.), заверение печатью (при наличии) (приказ № 406н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель (работодатель)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики (приложение № 1 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Уведомление организации, проводившей СОУТ, об утверждении отчета и направление копии утвержденного отчета</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Сведения об утверждении отчета; копия утвержденного отчета</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Работодатель</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>УКЭП</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ст. 4 ч. 2 п. 4, ст. 5 ч. 2, ст. 15 ч. 5 ФЗ-426</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Документ (лист) ознакомления работников с результатами СОУТ</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Факт ознакомления работника с результатами СОУТ на его рабочем месте; дата; подпись работника</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СОУТ подписанты" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'СОУТ подписанты'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$J$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,12 +28,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -46,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +72,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -441,22 +442,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="55" customHeight="1">
+    <row r="1" ht="45" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№ п/п</t>
@@ -508,7 +509,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -539,7 +540,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Состав комиссии (нечётное число); порядок деятельности комиссии; председатель; представители работодателя (включая специалиста по ОТ); представители выборного органа профсоюза / иного представительного органа работников (при наличии)</t>
+          <t>Состав комиссии (нечётное число); порядок деятельности комиссии; председатель; представители работодателя (включая специалиста по ОТ); представители выборного органа первичной профсоюзной организации / иного представительного органа работников (при наличии)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -558,7 +559,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -608,7 +609,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -658,7 +659,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -708,7 +709,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -739,7 +740,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения СОУТ; обязательства по предоставлению сведений, документов и информации об условиях труда</t>
+          <t>Условия проведения СОУТ; обязательства по предоставлению сведений, документов и информации об условиях труда; основание для получения идентификационного номера в ФГИС СОУТ</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -758,7 +759,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -789,7 +790,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения СОУТ; обязательства по предоставлению сведений, документов и информации об условиях труда</t>
+          <t>Условия проведения СОУТ; обязательства по предоставлению сведений, документов и информации об условиях труда; основание для получения идентификационного номера в ФГИС СОУТ</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -808,7 +809,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -824,12 +825,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н) — результаты идентификации оформляются экспертом; по результатам идентификации оформляется заключение</t>
+          <t>ст. 8 ч. 6 ФЗ-426; п. 3 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
+          <t>Уведомление о получении идентификационного номера предстоящей СОУТ</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -839,17 +840,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Результаты идентификации; при несовпадении наименований факторов с классификатором — фиксация отсутствия на РМ вредных и (или) опасных факторов, предусмотренных классификатором</t>
+          <t>Идентификационный номер предстоящей СОУТ, полученный в ФГИС учета результатов СОУТ; направляется работодателю до начала работ (на бумаге / заказным письмом / лично / электронным документом)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Уполномоченное лицо организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>УКЭП (при направлении в форме электронного документа — прямо указано в п. 3 Методики); на бумажном носителе — Нет требований</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -858,7 +859,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -874,12 +875,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н) — решения комиссии оформляются протоколом заседания</t>
+          <t>ст. 10 ФЗ-426; п. 6, 10 Методики — результаты идентификации оформляются экспертом; по результатам идентификации оформляется заключение</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по проведению СОУТ (решения комиссии)</t>
+          <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -889,12 +890,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в т.ч. о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
+          <t>Результаты идентификации (сопоставление с классификатором, приложение № 2 к приказу № 817н); при несовпадении наименований факторов с классификатором — фиксация отсутствия на РМ вредных и (или) опасных факторов, предусмотренных классификатором; основание для решений комиссии</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Эксперт организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -908,7 +909,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -924,7 +925,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н) — решения комиссии оформляются протоколом заседания</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики — решения комиссии оформляются протоколом заседания</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -939,12 +940,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в т.ч. о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
+          <t>Решения комиссии (в т.ч. утверждение результатов идентификации, о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -958,7 +959,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -974,12 +975,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики — решения комиссии оформляются протоколом заседания</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
+          <t>Протокол заседания комиссии по проведению СОУТ (решения комиссии)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -989,12 +990,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Перечень факторов, подлежащих исследованиям (испытаниям) и измерениям, исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемых оборудования, материалов и сырья</t>
+          <t>Решения комиссии (в т.ч. утверждение результатов идентификации, о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1008,7 +1009,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1024,7 +1025,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1039,12 +1040,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Перечень факторов, подлежащих исследованиям (испытаниям) и измерениям, исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемых оборудования, материалов и сырья</t>
+          <t>Перечень факторов исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемого оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1058,7 +1059,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
+    <row r="13">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1074,12 +1075,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1089,12 +1090,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер РМ, должность/профессия/специальность; наименование фактора по классификатору; дата исследований/измерений; сведения о средствах измерений; методики (методы) измерений и реквизиты утвердивших их актов; реквизиты актов о ПДК/ПДУ/нормативах; место измерений (при необходимости — эскиз); нормативные и фактические значения, продолжительность воздействия; заключение по фактическому уровню фактора с итоговым классом (подклассом); ФИО и должности специалистов, проводивших исследования (испытания) и измерения (п. 20 Методики, приложение № 1 к приказу № 817н)</t>
+          <t>Перечень факторов исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемого оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1108,7 +1109,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1124,12 +1125,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.1 классификатора (приложение № 2 к приказу № 817н); разд. IV Методики</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта о возможности использования результатов производственного контроля (при наличии)</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — параметры микроклимата</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1139,12 +1140,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной ИЛ (центром) при производственном контроле; прилагается к протоколу</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: параметры микроклимата.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1158,7 +1159,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1174,27 +1175,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 5 ФЗ-426; форма отчета / Методика (приказ № 817н)</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.2 классификатора; п. 41–47 Методики</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Протокол оценки эффективности средств индивидуальной защиты (при проведении такой оценки)</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — аэрозоли преимущественно фиброгенного действия (АПФД)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: аэрозоли преимущественно фиброгенного действия (АПФД).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1208,7 +1209,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1224,12 +1225,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.1 классификатора; п. 48–49 Методики</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — шум</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1239,12 +1240,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: шум.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1258,7 +1259,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1274,12 +1275,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.2 классификатора; п. 50–52 Методики</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — инфразвук</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1289,12 +1290,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: инфразвук.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1308,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
+    <row r="18">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1324,41 +1325,41 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.3 классификатора; п. 53 Методики</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — ультразвук воздушный</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: ультразвук воздушный.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1374,41 +1375,41 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.4 классификатора; п. 54–56 Методики</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — вибрация общая</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: вибрация общая.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1424,27 +1425,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.5 классификатора; п. 54–56 Методики</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — вибрация локальная</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: вибрация локальная.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Руководитель организации, проводящей СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1454,11 +1455,11 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -1474,27 +1475,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.4 классификатора; Методика по световой среде</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — параметры световой среды (освещенность рабочей поверхности)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: параметры световой среды (освещенность рабочей поверхности).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1504,11 +1505,11 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -1524,27 +1525,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.5 классификатора; Методика по неионизирующим излучениям</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — неионизирующие излучения</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: неионизирующие излучения.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1558,7 +1559,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -1574,27 +1575,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.6 классификатора; Методика по ионизирующим излучениям</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — ионизирующие излучения</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: ионизирующие излучения.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1608,7 +1609,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="48" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -1624,27 +1625,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 2 классификатора; п. 26–34 Методики</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — химический фактор</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: химический фактор.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1658,7 +1659,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1">
+    <row r="25">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -1674,32 +1675,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 3 классификатора; п. 35–40 Методики</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — биологический фактор</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: биологический фактор.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Работник, занятый на данном рабочем месте</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1708,7 +1709,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -1724,27 +1725,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 4 классификатора; Методика по тяжести</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — тяжесть трудового процесса</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: тяжесть трудового процесса.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1758,7 +1759,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
+    <row r="27">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -1774,27 +1775,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 5 классификатора; Методика по напряженности</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — напряженность трудового процесса</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: напряженность трудового процесса.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1808,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
+    <row r="28">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -1824,22 +1825,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н</t>
+          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Заключение эксперта о возможности использования результатов производственного контроля (при наличии)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при производственном контроле за условиями труда; прилагается к соответствующему протоколу</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1858,7 +1859,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
+    <row r="29">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -1874,27 +1875,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
+          <t>ст. 14 ч. 6–9, ст. 15 ч. 1 п. 5 ФЗ-426; Методика п. 106</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Протокол оценки эффективности средств индивидуальной защиты (при проведении такой оценки)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Результаты оценки эффективности применяемых работниками СИЗ, прошедших обязательную сертификацию, в целях снижения класса (подкласса) условий труда; составляется при проведении такой оценки и включается в отчет</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Эксперт организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1908,7 +1909,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="48" customHeight="1">
+    <row r="30">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -1924,27 +1925,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений (угроза жизни работника, экспертов и иных лиц); является неотъемлемой частью отчета; условия труда относятся к опасному классу без измерений</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1958,7 +1959,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="48" customHeight="1">
+    <row r="31">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -1974,27 +1975,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений (угроза жизни работника, экспертов и иных лиц); является неотъемлемой частью отчета; условия труда относятся к опасному классу без измерений</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Член комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2008,7 +2009,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1">
+    <row r="32">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -2024,27 +2025,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 9 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 12 ч. 11 ФЗ-426; п. 24 Методики</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта организации, проводящей СОУТ</t>
+          <t>Направление в территориальный орган Роструда копии протокола комиссии о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Копия протокола комиссии с решением о невозможности измерений; срок — в течение 10 рабочих дней со дня принятия решения; направляется по месту нахождения работодателя</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Работодатель</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2058,7 +2059,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1">
+    <row r="33">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -2069,46 +2070,46 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Письменные замечания и возражения работника относительно результатов СОУТ (при наличии)</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Замечания и возражения работника относительно результатов СОУТ на его рабочем месте</t>
+          <t>Не требуется (форма утверждена). Включает результаты по ст. 15 ч. 1 п. 1–10 ФЗ-426; на титульном листе — идентификационный номер (ст. 15 ч. 1.1, ст. 8 ч. 6)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Председатель комиссии по СОУТ</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="48" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -2124,22 +2125,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11 Методики — особое мнение к протоколу заседания</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Мотивированное особое мнение члена комиссии по СОУТ (при наличии)</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Письменное мотивированное (аргументированное) особое мнение члена комиссии</t>
+          <t>Не требуется (форма утверждена). Включает результаты по ст. 15 ч. 1 п. 1–10 ФЗ-426; на титульном листе — идентификационный номер (ст. 15 ч. 1.1, ст. 8 ч. 6)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2149,16 +2150,16 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -2169,17 +2170,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи (приказ № 406н)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 3 Инструкции</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2189,26 +2190,26 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Не требуется (форма утверждена). Раздел I «Сведения об организации, проводящей СОУТ» подписывается руководителем организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Руководитель юридического лица (работодатель)</t>
+          <t>Руководитель организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Да — место печати (М.П.), заверение печатью (при наличии) (приказ № 406н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -2219,17 +2220,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи (приказ № 406н)</t>
+          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Отчет о проведении СОУТ</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2239,26 +2240,26 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена)</t>
+          <t>Не требуется (форма утверждена). Эксперт(ы) подписывают отчет в составе результатов СОУТ</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Индивидуальный предприниматель (работодатель)</t>
+          <t>Эксперт организации, проводящей СОУТ</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="48" customHeight="1">
+          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -2274,12 +2275,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1 п. 1 ФЗ-426</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Уведомление организации, проводившей СОУТ, об утверждении отчета и направление копии утвержденного отчета</t>
+          <t>Копии документов, подтверждающих соответствие организации, проводящей СОУТ, требованиям ст. 19 ФЗ-426 (приложение к отчету)</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2289,17 +2290,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Сведения об утверждении отчета; копия утвержденного отчета</t>
+          <t>Копии документов, подтверждающих соответствие организации требованиям ст. 19 ФЗ-426 (прилагаются к сведениям об организации в отчете)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Руководитель организации, проводящей СОУТ (как приложение к сведениям раздела I отчета)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2308,7 +2309,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="48" customHeight="1">
+    <row r="38">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -2324,42 +2325,942 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ст. 4 ч. 2 п. 4, ст. 5 ч. 2, ст. 15 ч. 5 ФЗ-426</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Карта специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Работник, занятый на данном рабочем месте</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Форма утверждена. Таблица 1 — количество РМ и работников по классам (подклассам); таблица 2 — по каждому РМ классы по факторам (химический, биологический, АПФД, шум, инфразвук, ультразвук, вибрация общая/локальная, неионизирующие/ионизирующие, микроклимат, световая среда, тяжесть, напряженность), итоговый класс, класс с учетом СИЗ, гарантии и компенсации</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Форма утверждена. Таблица 1 — количество РМ и работников по классам (подклассам); таблица 2 — по каждому РМ классы по факторам (химический, биологический, АПФД, шум, инфразвук, ультразвук, вибрация общая/локальная, неионизирующие/ионизирующие, микроклимат, световая среда, тяжесть, напряженность), итоговый класс, класс с учетом СИЗ, гарантии и компенсации</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Форма утверждена. Таблица 1 — количество РМ и работников по классам (подклассам); таблица 2 — по каждому РМ классы по факторам (химический, биологический, АПФД, шум, инфразвук, ультразвук, вибрация общая/локальная, неионизирующие/ионизирующие, микроклимат, световая среда, тяжесть, напряженность), итоговый класс, класс с учетом СИЗ, гарантии и компенсации</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Форма утверждена. Наименование структурного подразделения/РМ; наименование мероприятия; цель; срок выполнения; структурные подразделения, привлекаемые для выполнения; отметка о выполнении. Для аналогичных РМ — единый перечень мероприятий (ст. 16 ч. 3 ФЗ-426)</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Форма утверждена. Наименование структурного подразделения/РМ; наименование мероприятия; цель; срок выполнения; структурные подразделения, привлекаемые для выполнения; отметка о выполнении. Для аналогичных РМ — единый перечень мероприятий (ст. 16 ч. 3 ФЗ-426)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Форма утверждена. Наименование структурного подразделения/РМ; наименование мероприятия; цель; срок выполнения; структурные подразделения, привлекаемые для выполнения; отметка о выполнении. Для аналогичных РМ — единый перечень мероприятий (ст. 16 ч. 3 ФЗ-426)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 9 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Заключение эксперта организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Заключение эксперта по результатам СОУТ; включается в отчет (ст. 15 ч. 1 п. 9 ФЗ-426)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Письменные замечания и возражения работника относительно результатов СОУТ (при наличии)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Замечания и возражения работника относительно результатов СОУТ на его рабочем месте; прилагаются к отчету</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции; п. 11, 108 Методики</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Мотивированное особое мнение члена комиссии по СОУТ (при наличии)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Письменное мотивированное (аргументированное) особое мнение члена комиссии; прилагается к отчету / к протоколу заседания; на титульном листе отчета — пометка «особое мнение»</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по СОУТ</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики; форма и Порядок подачи (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена приказом № 406н). Подается в отношении РМ, где факторы не выявлены либо условия оптимальны/допустимы (за исключением РМ по ст. 10 ч. 6 ФЗ-426)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Руководитель юридического лица (работодатель)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Да — место печати (М.П.), заверение печатью (при наличии) (приказ № 406н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики; форма и Порядок подачи (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется (форма утверждена приказом № 406н). Подается в отношении РМ, где факторы не выявлены либо условия оптимальны/допустимы (за исключением РМ по ст. 10 ч. 6 ФЗ-426)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель (работодатель)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Уведомление организации, проводившей СОУТ, об утверждении отчета и направление копии утвержденного отчета</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Уведомление об утверждении отчета (любым способом с подтверждением факта); копия утвержденного отчета — в течение 3 рабочих дней со дня утверждения</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Работодатель</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>УКЭП (для электронной копии утвержденного отчета — ст. 15 ч. 5.1 ФЗ-426); для уведомления на бумаге — Нет требований</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ст. 4 ч. 2 п. 4, ст. 5 ч. 2, ст. 15 ч. 5 ФЗ-426; п. 5 Инструкции (ознакомление также в Карте)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Документ (лист) ознакомления работников с результатами СОУТ</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Факт ознакомления работника с результатами СОУТ на его рабочем месте; дата; подпись работника</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Факт ознакомления работника с результатами СОУТ на его рабочем месте; дата; подпись работника. Срок ознакомления — не позднее 30 календарных дней со дня утверждения отчета (ст. 15 ч. 5). Ознакомление также оформляется в Карте СОУТ</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Работник</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 6 ФЗ-426</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Размещение сводных данных о результатах СОУТ на официальном сайте работодателя (при наличии сайта)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Сводные данные о результатах СОУТ в части установления классов (подклассов) условий труда на рабочих местах и перечня мероприятий по улучшению условий и охраны труда; срок — в течение 30 календарных дней со дня утверждения отчета</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Работодатель (уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>ст. 18 ФЗ-426</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Передача сведений о результатах СОУТ в Федеральную государственную информационную систему учета результатов проведения СОУТ</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Сведения о результатах СОУТ (в т.ч. по декларируемым РМ), за исключением сведений, составляющих охраняемую законом тайну; передача организацией, проводящей СОУТ, в порядке ст. 18 ФЗ-426</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Уполномоченное лицо организации, проводящей СОУТ</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J38"/>
+  <autoFilter ref="A1:J56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$J$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,22 +442,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№ п/п</t>
@@ -485,7 +485,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Унифицированная форма (да/нет)</t>
+          <t>Унифицированная форма (ДА/НЕТ)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Наличие реквизита в документе, который ограничивает электронную форму документа (например место печати)</t>
+          <t>Наличие реквизита, ограничивающего электронную форму документа (ДА/НЕТ)</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Приказ (распоряжение) о создании комиссии по проведению СОУТ</t>
+          <t>Приказ (распоряжение) о создании комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Состав комиссии (нечётное число); порядок деятельности комиссии; председатель; представители работодателя (включая специалиста по ОТ); представители выборного органа первичной профсоюзной организации / иного представительного органа работников (при наличии)</t>
+          <t>Состав комиссии (нечётное число членов); порядок деятельности комиссии; председатель комиссии; представители работодателя (в том числе специалист по охране труда); представители выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -580,12 +580,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>График проведения СОУТ</t>
+          <t>График проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -630,22 +630,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, подлежащих СОУТ</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться СОУТ; указание аналогичных рабочих мест</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -680,22 +680,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, подлежащих СОУТ</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться СОУТ; указание аналогичных рабочих мест</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -730,22 +730,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Гражданско-правовой договор с организацией, проводящей СОУТ</t>
+          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения СОУТ; обязательства по предоставлению сведений, документов и информации об условиях труда; основание для получения идентификационного номера в ФГИС СОУТ</t>
+          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -780,22 +780,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Гражданско-правовой договор с организацией, проводящей СОУТ</t>
+          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения СОУТ; обязательства по предоставлению сведений, документов и информации об условиях труда; основание для получения идентификационного номера в ФГИС СОУТ</t>
+          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Уполномоченное лицо организации, проводящей СОУТ</t>
+          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -830,32 +830,32 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Уведомление о получении идентификационного номера предстоящей СОУТ</t>
+          <t>Уведомление о получении идентификационного номера предстоящей специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Идентификационный номер предстоящей СОУТ, полученный в ФГИС учета результатов СОУТ; направляется работодателю до начала работ (на бумаге / заказным письмом / лично / электронным документом)</t>
+          <t>Идентификационный номер предстоящей специальной оценки условий труда, полученный в Федеральной государственной информационной системе учета результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Уполномоченное лицо организации, проводящей СОУТ</t>
+          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>УКЭП (при направлении в форме электронного документа — прямо указано в п. 3 Методики); на бумажном носителе — Нет требований</t>
+          <t>УКЭП</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ФЗ-426; п. 6, 10 Методики — результаты идентификации оформляются экспертом; по результатам идентификации оформляется заключение</t>
+          <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Результаты идентификации (сопоставление с классификатором, приложение № 2 к приказу № 817н); при несовпадении наименований факторов с классификатором — фиксация отсутствия на РМ вредных и (или) опасных факторов, предусмотренных классификатором; основание для решений комиссии</t>
+          <t>Результаты идентификации потенциально вредных и (или) опасных производственных факторов; при несовпадении наименований факторов с классификатором — фиксация отсутствия на рабочем месте вредных и (или) опасных производственных факторов, предусмотренных классификатором</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -925,27 +925,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики — решения комиссии оформляются протоколом заседания</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по проведению СОУТ (решения комиссии)</t>
+          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в т.ч. утверждение результатов идентификации, о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
+          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -975,27 +975,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики — решения комиссии оформляются протоколом заседания</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по проведению СОУТ (решения комиссии)</t>
+          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в т.ч. утверждение результатов идентификации, о проведении исследований/измерений); особое мнение членов комиссии, не согласных с решением (при наличии), приобщается к протоколу</t>
+          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1035,17 +1035,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Перечень факторов исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемого оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Перечень факторов исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производства, применяемого оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1125,27 +1125,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.1 классификатора (приложение № 2 к приказу № 817н); разд. IV Методики</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — параметры микроклимата</t>
+          <t>Протоколы проведения исследований (испытаний) и измерений идентифицированных вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: параметры микроклимата.</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) протокол оформляется в отношении каждого вредного и (или) опасного фактора и содержит: полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер рабочего места, должность (профессия, специальность) работника; наименование фактора по классификатору; дату проведения; сведения о средствах измерений; наименования методик (методов) измерений и реквизиты утвердивших их НПА; реквизиты НПА, регламентирующих ПДК (ПДУ, нормативные уровни); место проведения (при необходимости — эскиз); нормативное и фактическое значение уровня фактора; заключение по фактическому уровню с указанием класса (подкласса) условий труда по фактору; фамилии, имена, отчества (при наличии) и должности лиц, проводивших исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Эксперт и (или) иной работник организации, проводящей специальную оценку условий труда, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1175,27 +1175,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.2 классификатора; п. 41–47 Методики</t>
+          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — аэрозоли преимущественно фиброгенного действия (АПФД)</t>
+          <t>Заключение эксперта о возможности использования результатов производственного контроля</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: аэрозоли преимущественно фиброгенного действия (АПФД).</t>
+          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при осуществлении производственного контроля за условиями труда; прилагается к протоколу</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1225,27 +1225,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.1 классификатора; п. 48–49 Методики</t>
+          <t>ст. 14, ст. 15 ч. 1 п. 5 ФЗ-426; п. 106 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — шум</t>
+          <t>Протокол оценки эффективности средств индивидуальной защиты</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: шум.</t>
+          <t>Результаты оценки эффективности применяемых работниками, занятыми на рабочих местах с вредными условиями труда, средств индивидуальной защиты, прошедших обязательную сертификацию, проводимой в целях снижения класса (подкласса) условий труда (при проведении такой оценки)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1275,27 +1275,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.2 классификатора; п. 50–52 Методики</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — инфразвук</t>
+          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: инфразвук.</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1325,27 +1325,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.3 классификатора; п. 53 Методики</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — ультразвук воздушный</t>
+          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: ультразвук воздушный.</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1375,37 +1375,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.4 классификатора; п. 54–56 Методики</t>
+          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — вибрация общая</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: вибрация общая.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>ДА</t>
         </is>
       </c>
     </row>
@@ -1425,37 +1425,37 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.3.5 классификатора; п. 54–56 Методики</t>
+          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — вибрация локальная</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: вибрация локальная.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>ДА</t>
         </is>
       </c>
     </row>
@@ -1475,27 +1475,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.4 классификатора; Методика по световой среде</t>
+          <t>ст. 15 ч. 1 п. 1 ФЗ-426; п. 3 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — параметры световой среды (освещенность рабочей поверхности)</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: параметры световой среды (освещенность рабочей поверхности).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Руководитель организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>ДА</t>
         </is>
       </c>
     </row>
@@ -1525,27 +1525,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.5 классификатора; Методика по неионизирующим излучениям</t>
+          <t>ст. 15 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — неионизирующие излучения</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: неионизирующие излучения.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>ДА</t>
         </is>
       </c>
     </row>
@@ -1575,27 +1575,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 1.6 классификатора; Методика по ионизирующим излучениям</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — ионизирующие излучения</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: ионизирующие излучения.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1625,27 +1625,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 2 классификатора; п. 26–34 Методики</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — химический фактор</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: химический фактор.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1675,27 +1675,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 3 классификатора; п. 35–40 Методики</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — биологический фактор</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: биологический фактор.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1725,37 +1725,37 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 4 классификатора; Методика по тяжести</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — тяжесть трудового процесса</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: тяжесть трудового процесса.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1775,27 +1775,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (протокол оформляется в отношении каждого фактора); п. 5 классификатора; Методика по напряженности</t>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Протокол исследований (испытаний) и измерений вредных и (или) опасных производственных факторов — напряженность трудового процесса</t>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) — отдельный протокол на каждый фактор: 1) полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; 2) уникальный номер протокола на каждой странице вместе с номером страницы; 3) полное наименование работодателя; 4) адрес места нахождения и адрес места осуществления деятельности работодателя; 5) наименование структурного подразделения (при наличии); 6) индивидуальный номер РМ, должность/профессия/специальность работника; 7) наименование вредного и (или) опасного фактора по классификатору; 8) дата проведения исследований (испытаний) и измерений; 9) сведения о средствах измерений (наименование, заводской номер, срок и номер свидетельства о поверке); 10) наименования методик (методов) измерений и реквизиты НПА, их утвердивших; 11) реквизиты НПА, регламентирующих ПДК/ПДУ/нормативные уровни; 12) место проведения с приложением при необходимости эскиза помещения и точек измерений; 13) нормативное и фактическое значение уровня фактора (при необходимости — единицы и продолжительность воздействия); 14) заключение по фактическому уровню с указанием итогового класса (подкласса) условий труда по фактору; 15) ФИО и должности специалистов, проводивших исследования (испытания) и измерения. Фактор настоящего протокола: напряженность трудового процесса.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Специалист организации, проводящей СОУТ, проводивший исследования (испытания) и измерения</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1825,27 +1825,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики</t>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта о возможности использования результатов производственного контроля (при наличии)</t>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при производственном контроле за условиями труда; прилагается к соответствующему протоколу</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1875,27 +1875,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ст. 14 ч. 6–9, ст. 15 ч. 1 п. 5 ФЗ-426; Методика п. 106</t>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Протокол оценки эффективности средств индивидуальной защиты (при проведении такой оценки)</t>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Результаты оценки эффективности применяемых работниками СИЗ, прошедших обязательную сертификацию, в целях снижения класса (подкласса) условий труда; составляется при проведении такой оценки и включается в отчет</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1925,27 +1925,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики</t>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений (угроза жизни работника, экспертов и иных лиц); является неотъемлемой частью отчета; условия труда относятся к опасному классу без измерений</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -1975,27 +1975,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики</t>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии о невозможности проведения исследований (испытаний) и измерений (при наличии)</t>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений (угроза жизни работника, экспертов и иных лиц); является неотъемлемой частью отчета; условия труда относятся к опасному классу без измерений</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -2025,27 +2025,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 11 ФЗ-426; п. 24 Методики</t>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Направление в территориальный орган Роструда копии протокола комиссии о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Копия протокола комиссии с решением о невозможности измерений; срок — в течение 10 рабочих дней со дня принятия решения; направляется по месту нахождения работодателя</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -2075,37 +2075,37 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
+          <t>ст. 15 ч. 1 п. 9 ФЗ-426</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Заключения эксперта организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена). Включает результаты по ст. 15 ч. 1 п. 1–10 ФЗ-426; на титульном листе — идентификационный номер (ст. 15 ч. 1.1, ст. 8 ч. 6)</t>
+          <t>Заключения эксперта организации, проводящей специальную оценку условий труда, по результатам ее проведения</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -2120,42 +2120,42 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
+          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена). Включает результаты по ст. 15 ч. 1 п. 1–10 ФЗ-426; на титульном листе — идентификационный номер (ст. 15 ч. 1.1, ст. 8 ч. 6)</t>
+          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда, проведенной на его рабочем месте, в письменном виде</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по СОУТ</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -2175,27 +2175,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 3 Инструкции</t>
+          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11, 108 Методики</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Мотивированное особое мнение члена комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена). Раздел I «Сведения об организации, проводящей СОУТ» подписывается руководителем организации, проводящей СОУТ</t>
+          <t>Мотивированное (аргументированное) особое мнение члена комиссии в письменной форме; прилагается к отчету о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Руководитель организации, проводящей СОУТ</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
@@ -2220,42 +2220,42 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3, 5 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении СОУТ</t>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Не требуется (форма утверждена). Эксперт(ы) подписывают отчет в составе результатов СОУТ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
+          <t>Руководитель юридического лица (работодатель)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или УКЭП</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Да — заверение печатью организации, проводящей СОУТ (при наличии) (п. 3 Инструкции, приложение № 4 к приказу № 817н)</t>
+          <t>ДА</t>
         </is>
       </c>
     </row>
@@ -2270,42 +2270,42 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 1 ФЗ-426</t>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Копии документов, подтверждающих соответствие организации, проводящей СОУТ, требованиям ст. 19 ФЗ-426 (приложение к отчету)</t>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Копии документов, подтверждающих соответствие организации требованиям ст. 19 ФЗ-426 (прилагаются к сведениям об организации в отчете)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Руководитель организации, проводящей СОУТ (как приложение к сведениям раздела I отчета)</t>
+          <t>Индивидуальный предприниматель (работодатель)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или УКЭП</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>ДА</t>
         </is>
       </c>
     </row>
@@ -2320,32 +2320,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
+          <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Уведомление организации, проводившей специальную оценку условий труда, об утверждении отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
+          <t>Сведения об утверждении отчета о проведении специальной оценки условий труда; способ уведомления должен обеспечивать возможность подтверждения факта уведомления</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по СОУТ</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2355,912 +2355,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Карта специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Карта специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции (приложение № 4) — Карта подписывается председателем, членами комиссии, экспертом (экспертами) и работниками, занятыми на данном РМ</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Карта специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Форма — раздел III приложения № 3 к приказу № 817н. По п. 5 Инструкции (приложение № 4): сведения о работодателе; должность/профессия/специальность и код; структурное подразделение; количество и номера аналогичных РМ; строки 010–011 (ЕТКС/ЕКС/профстандарт, код ОК 016-94); 020 — численность работников (в т.ч. женщины, до 18 лет, инвалиды); 021 — СНИЛС; 022 — оборудование, материалы и сырье; 030 — классы (подклассы) по факторам, оценка эффективности СИЗ, итоговый класс; 040 — гарантии и компенсации (факт / необходимость / основание); 050 — рекомендации; дата составления. На аналогичные РМ заполняется одна карта (ст. 16 ч. 2 ФЗ-426).</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Работник, занятый на данном рабочем месте</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Форма утверждена. Таблица 1 — количество РМ и работников по классам (подклассам); таблица 2 — по каждому РМ классы по факторам (химический, биологический, АПФД, шум, инфразвук, ультразвук, вибрация общая/локальная, неионизирующие/ионизирующие, микроклимат, световая среда, тяжесть, напряженность), итоговый класс, класс с учетом СИЗ, гарантии и компенсации</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Форма утверждена. Таблица 1 — количество РМ и работников по классам (подклассам); таблица 2 — по каждому РМ классы по факторам (химический, биологический, АПФД, шум, инфразвук, ультразвук, вибрация общая/локальная, неионизирующие/ионизирующие, микроклимат, световая среда, тяжесть, напряженность), итоговый класс, класс с учетом СИЗ, гарантии и компенсации</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Форма утверждена. Таблица 1 — количество РМ и работников по классам (подклассам); таблица 2 — по каждому РМ классы по факторам (химический, биологический, АПФД, шум, инфразвук, ультразвук, вибрация общая/локальная, неионизирующие/ионизирующие, микроклимат, световая среда, тяжесть, напряженность), итоговый класс, класс с учетом СИЗ, гарантии и компенсации</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Форма утверждена. Наименование структурного подразделения/РМ; наименование мероприятия; цель; срок выполнения; структурные подразделения, привлекаемые для выполнения; отметка о выполнении. Для аналогичных РМ — единый перечень мероприятий (ст. 16 ч. 3 ФЗ-426)</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Форма утверждена. Наименование структурного подразделения/РМ; наименование мероприятия; цель; срок выполнения; структурные подразделения, привлекаемые для выполнения; отметка о выполнении. Для аналогичных РМ — единый перечень мероприятий (ст. 16 ч. 3 ФЗ-426)</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Форма утверждена. Наименование структурного подразделения/РМ; наименование мероприятия; цель; срок выполнения; структурные подразделения, привлекаемые для выполнения; отметка о выполнении. Для аналогичных РМ — единый перечень мероприятий (ст. 16 ч. 3 ФЗ-426)</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 1 п. 9 ФЗ-426; Методика (приложение № 1 к приказу № 817н)</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Заключение эксперта организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Заключение эксперта по результатам СОУТ; включается в отчет (ст. 15 ч. 1 п. 9 ФЗ-426)</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Эксперт организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Письменные замечания и возражения работника относительно результатов СОУТ (при наличии)</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Замечания и возражения работника относительно результатов СОУТ на его рабочем месте; прилагаются к отчету</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Работник</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции; п. 11, 108 Методики</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Мотивированное особое мнение члена комиссии по СОУТ (при наличии)</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Письменное мотивированное (аргументированное) особое мнение члена комиссии; прилагается к отчету / к протоколу заседания; на титульном листе отчета — пометка «особое мнение»</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Член комиссии по СОУТ</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики; форма и Порядок подачи (приказ № 406н)</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена приказом № 406н). Подается в отношении РМ, где факторы не выявлены либо условия оптимальны/допустимы (за исключением РМ по ст. 10 ч. 6 ФЗ-426)</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Руководитель юридического лица (работодатель)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>Да — место печати (М.П.), заверение печатью (при наличии) (приказ № 406н)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики; форма и Порядок подачи (приказ № 406н)</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Не требуется (форма утверждена приказом № 406н). Подается в отношении РМ, где факторы не выявлены либо условия оптимальны/допустимы (за исключением РМ по ст. 10 ч. 6 ФЗ-426)</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Индивидуальный предприниматель (работодатель)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Уведомление организации, проводившей СОУТ, об утверждении отчета и направление копии утвержденного отчета</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Уведомление об утверждении отчета (любым способом с подтверждением факта); копия утвержденного отчета — в течение 3 рабочих дней со дня утверждения</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Работодатель</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>УКЭП (для электронной копии утвержденного отчета — ст. 15 ч. 5.1 ФЗ-426); для уведомления на бумаге — Нет требований</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>ст. 4 ч. 2 п. 4, ст. 5 ч. 2, ст. 15 ч. 5 ФЗ-426; п. 5 Инструкции (ознакомление также в Карте)</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Документ (лист) ознакомления работников с результатами СОУТ</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Факт ознакомления работника с результатами СОУТ на его рабочем месте; дата; подпись работника. Срок ознакомления — не позднее 30 календарных дней со дня утверждения отчета (ст. 15 ч. 5). Ознакомление также оформляется в Карте СОУТ</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Работник</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>ст. 15 ч. 6 ФЗ-426</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Размещение сводных данных о результатах СОУТ на официальном сайте работодателя (при наличии сайта)</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Сводные данные о результатах СОУТ в части установления классов (подклассов) условий труда на рабочих местах и перечня мероприятий по улучшению условий и охраны труда; срок — в течение 30 календарных дней со дня утверждения отчета</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Работодатель (уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>СОУТ</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>ст. 18 ФЗ-426</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Передача сведений о результатах СОУТ в Федеральную государственную информационную систему учета результатов проведения СОУТ</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Сведения о результатах СОУТ (в т.ч. по декларируемым РМ), за исключением сведений, составляющих охраняемую законом тайну; передача организацией, проводящей СОУТ, в порядке ст. 18 ФЗ-426</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Уполномоченное лицо организации, проводящей СОУТ</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>НЕТ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J56"/>
+  <autoFilter ref="A1:J38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,7 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
@@ -508,6 +509,11 @@
           <t>Наличие реквизита, ограничивающего электронную форму документа (ДА/НЕТ)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Сведения о реквизите, ограничивающем электронную форму документа</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -558,6 +564,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -608,6 +619,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -658,6 +674,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -708,6 +729,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -758,6 +784,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -808,6 +839,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -858,6 +894,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -908,6 +949,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -958,6 +1004,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1008,6 +1059,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1058,6 +1114,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1108,6 +1169,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1158,6 +1224,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1208,6 +1279,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1258,6 +1334,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1308,6 +1389,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1358,6 +1444,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1408,6 +1499,11 @@
           <t>ДА</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1458,6 +1554,11 @@
           <t>ДА</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1508,6 +1609,11 @@
           <t>ДА</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1558,6 +1664,11 @@
           <t>ДА</t>
         </is>
       </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1608,6 +1719,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1658,6 +1774,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1708,6 +1829,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1758,6 +1884,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1808,6 +1939,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1858,6 +1994,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1908,6 +2049,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1958,6 +2104,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2008,6 +2159,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2058,6 +2214,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2108,6 +2269,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2158,6 +2324,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2208,6 +2379,11 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2258,6 +2434,11 @@
           <t>ДА</t>
         </is>
       </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2308,6 +2489,11 @@
           <t>ДА</t>
         </is>
       </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2358,9 +2544,14 @@
           <t>НЕТ</t>
         </is>
       </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J38"/>
+  <autoFilter ref="A1:K38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$K$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$K$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -521,22 +521,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ; Приказ Минтруда России от 29.10.2021 № 776н</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 1, 2 ФЗ-426</t>
+          <t>ст. 214, ст. 217 ТК РФ; п. 1 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Приказ (распоряжение) о создании комиссии по проведению специальной оценки условий труда</t>
+          <t>Положение о системе управления охраной труда</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Состав комиссии (нечётное число членов); порядок деятельности комиссии; председатель комиссии; представители работодателя (в том числе специалист по охране труда); представители выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии)</t>
+          <t>Политика и цели в области охраны труда; структура и порядок функционирования системы управления охраной труда; процедуры (процессы) СУОТ, включая специальную оценку условий труда как базовый процесс; распределение обязанностей, ответственности и полномочий в области охраны труда; порядок планирования, контроля и улучшения функционирования СУОТ (с учетом Примерного положения, утвержденного приказом Минтруда России № 776н)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -576,22 +576,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 1 ФЗ-426</t>
+          <t>ст. 214 ТК РФ (разработка и утверждение локальных нормативных актов по охране труда с учетом мнения); ст. 372 ТК РФ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>График проведения специальной оценки условий труда</t>
+          <t>Мотивированное мнение выборного органа первичной профсоюзной организации (иного представительного органа работников) при принятии Положения о системе управления охраной труда</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Сроки (этапы) проведения специальной оценки условий труда</t>
+          <t>Мотивированное мнение по проекту локального нормативного акта (Положения о СУОТ) в порядке ст. 372 ТК РФ</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации или иной представительный орган работников (при наличии)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 214 ТК РФ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
+          <t>Реестр (перечень) нормативных правовых актов, содержащих требования охраны труда</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
+          <t>Перечень нормативных правовых актов (в том числе с использованием ЭВМ и баз данных), содержащих требования охраны труда, в соответствии со спецификой деятельности работодателя; обеспечение доступа работников к актуальным редакциям</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -686,22 +686,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 223 ТК РФ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
+          <t>Приказ (распоряжение) о создании службы охраны труда или о введении должности специалиста по охране труда</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
+          <t>Решение о создании службы охраны труда либо о введении должности специалиста по охране труда; структура службы и численность работников службы (при создании службы)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
+          <t>ст. 224 ТК РФ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
+          <t>Положение о комитете (комиссии) по охране труда</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
+          <t>Цели, задачи и порядок работы комитета (комиссии) по охране труда; состав на паритетной основе; участие в проведении специальной оценки условий труда; участие в информировании работников о состоянии условий и охраны труда (с учетом Примерного положения о комитете (комиссии) по охране труда)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -796,22 +796,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
+          <t>ст. 224 ТК РФ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
+          <t>Приказ (распоряжение) о создании комитета (комиссии) по охране труда</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
+          <t>Создание комитета (комиссии) по охране труда; состав представителей работодателя и представителей выборного органа первичной профсоюзной организации или иного уполномоченного представительного органа работников (при наличии)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -851,22 +851,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ст. 8 ч. 6 ФЗ-426; п. 3 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 214.1 ТК РФ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Уведомление о получении идентификационного номера предстоящей специальной оценки условий труда</t>
+          <t>Приказ (распоряжение) о приостановлении работ на рабочих местах с опасным классом условий труда</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Идентификационный номер предстоящей специальной оценки условий труда, полученный в Федеральной государственной информационной системе учета результатов проведения специальной оценки условий труда</t>
+          <t>Приостановка работ на рабочих местах, условия труда на которых по результатам специальной оценки условий труда отнесены к опасному классу условий труда; срок (до устранения оснований опасного класса)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -906,22 +906,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 214.1 ТК РФ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
+          <t>План мероприятий по устранению оснований, послуживших установлению опасного класса условий труда</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Результаты идентификации потенциально вредных и (или) опасных производственных факторов; при несовпадении наименований факторов с классификатором — фиксация отсутствия на рабочем месте вредных и (или) опасных производственных факторов, предусмотренных классификатором</t>
+          <t>Мероприятия по устранению оснований, послуживших установлению опасного класса условий труда; разрабатывается работодателем с учетом мнения выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии); утверждается работодателем; копия направляется в территориальный орган Роструда</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -961,22 +961,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 214.1 ТК РФ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
+          <t>Мнение выборного органа первичной профсоюзной организации (иного представительного органа работников) при разработке плана мероприятий по устранению оснований опасного класса условий труда</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
+          <t>Мнение представительного органа работников, учитываемое при разработке плана мероприятий (ст. 214.1 ТК РФ)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Выборный орган первичной профсоюзной организации или иной представительный орган работников (при наличии)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 216.2 ТК РФ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
+          <t>Уведомление (информация) работника об отнесении условий труда на его рабочем месте к опасному классу условий труда</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
+          <t>Сведения об отнесении условий труда на рабочем месте работника по результатам специальной оценки условий труда к опасному классу условий труда; доводится работодателем незамедлительно</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 1, 2 ФЗ-426</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
+          <t>Приказ (распоряжение) о создании комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
+          <t>Состав комиссии (нечётное число членов); порядок деятельности комиссии; председатель комиссии; представители работодателя (в том числе специалист по охране труда); представители выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 1 ФЗ-426</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
+          <t>График проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
+          <t>Сроки (этапы) проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Протоколы проведения исследований (испытаний) и измерений идентифицированных вредных и (или) опасных производственных факторов</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) протокол оформляется в отношении каждого вредного и (или) опасного фактора и содержит: полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер рабочего места, должность (профессия, специальность) работника; наименование фактора по классификатору; дату проведения; сведения о средствах измерений; наименования методик (методов) измерений и реквизиты утвердивших их НПА; реквизиты НПА, регламентирующих ПДК (ПДУ, нормативные уровни); место проведения (при необходимости — эскиз); нормативное и фактическое значение уровня фактора; заключение по фактическому уровню с указанием класса (подкласса) условий труда по фактору; фамилии, имена, отчества (при наличии) и должности лиц, проводивших исследования (испытания) и измерения</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Эксперт и (или) иной работник организации, проводящей специальную оценку условий труда, проводивший исследования (испытания) и измерения</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта о возможности использования результатов производственного контроля</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при осуществлении производственного контроля за условиями труда; прилагается к протоколу</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ст. 14, ст. 15 ч. 1 п. 5 ФЗ-426; п. 106 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Протокол оценки эффективности средств индивидуальной защиты</t>
+          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Результаты оценки эффективности применяемых работниками, занятыми на рабочих местах с вредными условиями труда, средств индивидуальной защиты, прошедших обязательную сертификацию, проводимой в целях снижения класса (подкласса) условий труда (при проведении такой оценки)</t>
+          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
+          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 8 ч. 6 ФЗ-426; п. 3 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>Уведомление о получении идентификационного номера предстоящей специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
+          <t>Идентификационный номер предстоящей специальной оценки условий труда, полученный в Федеральной государственной информационной системе учета результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>УКЭП</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
+          <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Результаты идентификации потенциально вредных и (или) опасных производственных факторов; при несовпадении наименований факторов с классификатором — фиксация отсутствия на рабочем месте вредных и (или) опасных производственных факторов, предусмотренных классификатором</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1521,42 +1521,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1576,27 +1576,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 1 ФЗ-426; п. 3 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Руководитель организации, проводящей специальную оценку условий труда</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1631,27 +1631,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1686,27 +1686,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1741,27 +1741,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протоколы проведения исследований (испытаний) и измерений идентифицированных вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) протокол оформляется в отношении каждого вредного и (или) опасного фактора и содержит: полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер рабочего места, должность (профессия, специальность) работника; наименование фактора по классификатору; дату проведения; сведения о средствах измерений; наименования методик (методов) измерений и реквизиты утвердивших их НПА; реквизиты НПА, регламентирующих ПДК (ПДУ, нормативные уровни); место проведения (при необходимости — эскиз); нормативное и фактическое значение уровня фактора; заключение по фактическому уровню с указанием класса (подкласса) условий труда по фактору; фамилии, имена, отчества (при наличии) и должности лиц, проводивших исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Эксперт и (или) иной работник организации, проводящей специальную оценку условий труда, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Заключение эксперта о возможности использования результатов производственного контроля</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при осуществлении производственного контроля за условиями труда; прилагается к протоколу</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1851,32 +1851,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 14, ст. 15 ч. 1 п. 5 ФЗ-426; п. 106 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол оценки эффективности средств индивидуальной защиты</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Результаты оценки эффективности применяемых работниками, занятыми на рабочих местах с вредными условиями труда, средств индивидуальной защиты, прошедших обязательную сертификацию, проводимой в целях снижения класса (подкласса) условий труда (при проведении такой оценки)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1961,22 +1961,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2036,22 +2036,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2091,22 +2091,22 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1 п. 1 ФЗ-426; п. 3 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Руководитель организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2236,27 +2236,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 9 ФЗ-426</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Заключения эксперта организации, проводящей специальную оценку условий труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Заключения эксперта организации, проводящей специальную оценку условий труда, по результатам ее проведения</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2286,32 +2286,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда, проведенной на его рабочем месте, в письменном виде</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2346,27 +2346,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11, 108 Методики</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Мотивированное особое мнение члена комиссии по проведению специальной оценки условий труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Мотивированное (аргументированное) особое мнение члена комиссии в письменной форме; прилагается к отчету о проведении специальной оценки условий труда</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2421,22 +2421,22 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Руководитель юридического лица (работодатель)</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>собственноручная</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2451,17 +2451,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2476,22 +2476,22 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Индивидуальный предприниматель (работодатель)</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2506,52 +2506,602 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 9 ФЗ-426</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Заключения эксперта организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Заключения эксперта организации, проводящей специальную оценку условий труда, по результатам ее проведения</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда, проведенной на его рабочем месте, в письменном виде</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11, 108 Методики</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Мотивированное особое мнение члена комиссии по проведению специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Мотивированное (аргументированное) особое мнение члена комиссии в письменной форме; прилагается к отчету о проведении специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Руководитель юридического лица (работодатель)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель (работодатель)</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Уведомление организации, проводившей специальную оценку условий труда, об утверждении отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Сведения об утверждении отчета о проведении специальной оценки условий труда; способ уведомления должен обеспечивать возможность подтверждения факта уведомления</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K38"/>
+  <autoFilter ref="A1:K48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$K$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$K$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 1, 2 ФЗ-426</t>
+          <t>п. 9–11 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Приказ (распоряжение) о создании комиссии по проведению специальной оценки условий труда</t>
+          <t>Политика (стратегия) в области охраны труда</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Состав комиссии (нечётное число членов); порядок деятельности комиссии; председатель комиссии; представители работодателя (в том числе специалист по охране труда); представители выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии)</t>
+          <t>Цели и мероприятия, направленные на сохранение жизни и здоровья работников; публичная декларация работодателя о намерении выполнять государственные нормативные требования охраны труда и добровольно принятые обязательства; обеспечение безопасных условий труда; управление рисками; устранение опасностей и снижение уровней профессиональных рисков; обязательство совершенствовать СУОТ; учет мнения представительного органа работников (при наличии). Может оформляться отдельным локальным актом либо разделом локального акта работодателя</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1126,22 +1126,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 1 ФЗ-426</t>
+          <t>п. 9, 10 (ж) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>График проведения специальной оценки условий труда</t>
+          <t>Мнение выборного органа первичной профсоюзной организации (иного уполномоченного работниками органа) при принятии Политики (стратегии) в области охраны труда</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Сроки (этапы) проведения специальной оценки условий труда</t>
+          <t>Мнение представительного органа работников, учитываемое при принятии Политики (стратегии) в области охраны труда</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации или иной уполномоченный работниками представительный орган (при наличии)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>п. 12–13, п. 55 (ж) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
+          <t>Приказ (распоряжение) о назначении лиц, ответственных за соблюдение требований охраны труда и обеспечение функционирования СУОТ</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
+          <t>Назначение работников, ответственных за соблюдение требований охраны труда; предоставление полномочий для взаимодействия в рамках функционирования СУОТ (включая организацию и контроль базового процесса специальной оценки условий труда); документирование информации об ответственных лицах и их полномочиях</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>п. 29–32, п. 48, п. 55 (а) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
+          <t>План мероприятий по охране труда</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
+          <t>Наименование мероприятий; ожидаемый результат по каждому мероприятию; сроки реализации; ответственные лица; выделяемые ресурсы и источники финансирования. При составлении учитываются в том числе изменения условий труда по результатам специальной оценки условий труда (СОУТ) и оценки профессиональных рисков (ОПР)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
+          <t>п. 44–46, п. 55 (е) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
+          <t>Порядок (процедура) информирования работников и взаимодействия с работниками в рамках СУОТ</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
+          <t>Порядок информирования работников о политике и целях в области охраны труда, об опасностях и рисках, о мерах управления; формы доведения информации, включая ознакомление работника с результатами специальной оценки условий труда и оценки профессиональных рисков; порядок взаимодействия с работниками</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1346,22 +1346,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
+          <t>п. 60–63, п. 55 (в) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
+          <t>Порядок контроля и оценки результативности функционирования СУОТ</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
+          <t>Объекты, методы и критерии контроля; виды контроля, в том числе контроль выполнения процессов периодического характера, включая специальную оценку условий труда работников; порядок оценки соответствия условий и охраны труда требованиям и анализ показателей функционирования СУОТ</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1401,22 +1401,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ст. 8 ч. 6 ФЗ-426; п. 3 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>п. 63 (б), 67–69 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Уведомление о получении идентификационного номера предстоящей специальной оценки условий труда</t>
+          <t>Документы (информация) по результатам контроля функционирования СУОТ</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Идентификационный номер предстоящей специальной оценки условий труда, полученный в Федеральной государственной информационной системе учета результатов проведения специальной оценки условий труда</t>
+          <t>Результаты контроля, измерений, анализа и оценки показателей деятельности СУОТ, в том числе по контролю выполнения специальной оценки условий труда; информация фиксируется и сохраняется работодателем</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>п. 63 (б), 67–69 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
+          <t>Документы (информация) по результатам контроля функционирования СУОТ</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Результаты идентификации потенциально вредных и (или) опасных производственных факторов; при несовпадении наименований факторов с классификатором — фиксация отсутствия на рабочем месте вредных и (или) опасных производственных факторов, предусмотренных классификатором</t>
+          <t>Результаты контроля, измерений, анализа и оценки показателей деятельности СУОТ, в том числе по контролю выполнения специальной оценки условий труда; информация фиксируется и сохраняется работодателем</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Специалист по охране труда (уполномоченное лицо работодателя)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>СОУТ</t>
+          <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>п. 70–73, п. 55 (г) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
+          <t>Порядок формирования корректирующих действий по совершенствованию функционирования СУОТ</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
+          <t>Порядок разработки корректирующих действий по совершенствованию СУОТ на основе результатов выполнения мероприятий по охране труда, анализа по результатам контроля, расследований, предписаний, предложений работников; в том числе с учетом результатов специальной оценки условий труда как базового процесса СУОТ</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 1, 2 ФЗ-426</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
+          <t>Приказ (распоряжение) о создании комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
+          <t>Состав комиссии (нечётное число членов); порядок деятельности комиссии; председатель комиссии; представители работодателя (в том числе специалист по охране труда); представители выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1626,17 +1626,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 1 ФЗ-426</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
+          <t>График проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
+          <t>Сроки (этапы) проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Протоколы проведения исследований (испытаний) и измерений идентифицированных вредных и (или) опасных производственных факторов</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) протокол оформляется в отношении каждого вредного и (или) опасного фактора и содержит: полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер рабочего места, должность (профессия, специальность) работника; наименование фактора по классификатору; дату проведения; сведения о средствах измерений; наименования методик (методов) измерений и реквизиты утвердивших их НПА; реквизиты НПА, регламентирующих ПДК (ПДУ, нормативные уровни); место проведения (при необходимости — эскиз); нормативное и фактическое значение уровня фактора; заключение по фактическому уровню с указанием класса (подкласса) условий труда по фактору; фамилии, имена, отчества (при наличии) и должности лиц, проводивших исследования (испытания) и измерения</t>
+          <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Эксперт и (или) иной работник организации, проводящей специальную оценку условий труда, проводивший исследования (испытания) и измерения</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1791,17 +1791,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Заключение эксперта о возможности использования результатов производственного контроля</t>
+          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при осуществлении производственного контроля за условиями труда; прилагается к протоколу</t>
+          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ст. 14, ст. 15 ч. 1 п. 5 ФЗ-426; п. 106 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 8 ч. 2, 6 ФЗ-426</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Протокол оценки эффективности средств индивидуальной защиты</t>
+          <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Результаты оценки эффективности применяемых работниками, занятыми на рабочих местах с вредными условиями труда, средств индивидуальной защиты, прошедших обязательную сертификацию, проводимой в целях снижения класса (подкласса) условий труда (при проведении такой оценки)</t>
+          <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 8 ч. 6 ФЗ-426; п. 3 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>Уведомление о получении идентификационного номера предстоящей специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
+          <t>Идентификационный номер предстоящей специальной оценки условий труда, полученный в Федеральной государственной информационной системе учета результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>УКЭП</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
+          <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
+          <t>Результаты идентификации потенциально вредных и (или) опасных производственных факторов; при несовпадении наименований факторов с классификатором — фиксация отсутствия на рабочем месте вредных и (или) опасных производственных факторов, предусмотренных классификатором</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2016,22 +2016,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2041,17 +2041,17 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2071,22 +2071,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
+          <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или НЭП или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2126,27 +2126,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 1 ФЗ-426; п. 3 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Руководитель организации, проводящей специальную оценку условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2181,27 +2181,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
+          <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Отчет о проведении специальной оценки условий труда</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2236,27 +2236,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протоколы проведения исследований (испытаний) и измерений идентифицированных вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>По п. 20 Методики (приложение № 1 к приказу № 817н) протокол оформляется в отношении каждого вредного и (или) опасного фактора и содержит: полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер рабочего места, должность (профессия, специальность) работника; наименование фактора по классификатору; дату проведения; сведения о средствах измерений; наименования методик (методов) измерений и реквизиты утвердивших их НПА; реквизиты НПА, регламентирующих ПДК (ПДУ, нормативные уровни); место проведения (при необходимости — эскиз); нормативное и фактическое значение уровня фактора; заключение по фактическому уровню с указанием класса (подкласса) условий труда по фактору; фамилии, имена, отчества (при наличии) и должности лиц, проводивших исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Эксперт и (или) иной работник организации, проводящей специальную оценку условий труда, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2291,27 +2291,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Заключение эксперта о возможности использования результатов производственного контроля</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при осуществлении производственного контроля за условиями труда; прилагается к протоколу</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2346,22 +2346,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 14, ст. 15 ч. 1 п. 5 ФЗ-426; п. 106 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол оценки эффективности средств индивидуальной защиты</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Результаты оценки эффективности применяемых работниками, занятыми на рабочих местах с вредными условиями труда, средств индивидуальной защиты, прошедших обязательную сертификацию, проводимой в целях снижения класса (подкласса) условий труда (при проведении такой оценки)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Карта специальной оценки условий труда</t>
+          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2456,27 +2456,27 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2531,22 +2531,22 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2586,22 +2586,22 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1 п. 1 ФЗ-426; п. 3 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+          <t>Руководитель организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 1 п. 9 ФЗ-426</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Заключения эксперта организации, проводящей специальную оценку условий труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Заключения эксперта организации, проводящей специальную оценку условий труда, по результатам ее проведения</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2836,32 +2836,32 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда, проведенной на его рабочем месте, в письменном виде</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11, 108 Методики</t>
+          <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Мотивированное особое мнение члена комиссии по проведению специальной оценки условий труда</t>
+          <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Мотивированное (аргументированное) особое мнение члена комиссии в письменной форме; прилагается к отчету о проведении специальной оценки условий труда</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Член комиссии по проведению специальной оценки условий труда</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>собственноручная</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2971,22 +2971,22 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Руководитель юридического лица (работодатель)</t>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3001,17 +3001,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3026,22 +3026,22 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Индивидуальный предприниматель (работодатель)</t>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>собственноручная или УКЭП</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3056,52 +3056,547 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 1 п. 9 ФЗ-426</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Заключения эксперта организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Заключения эксперта организации, проводящей специальную оценку условий труда, по результатам ее проведения</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Эксперт организации, проводящей специальную оценку условий труда</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Замечания и возражения работника относительно результатов специальной оценки условий труда, проведенной на его рабочем месте, в письменном виде</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11, 108 Методики</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Мотивированное особое мнение члена комиссии по проведению специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Мотивированное (аргументированное) особое мнение члена комиссии в письменной форме; прилагается к отчету о проведении специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Член комиссии по проведению специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Руководитель юридического лица (работодатель)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Индивидуальный предприниматель (работодатель)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>СОУТ</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Уведомление организации, проводившей специальную оценку условий труда, об утверждении отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Сведения об утверждении отчета о проведении специальной оценки условий труда; способ уведомления должен обеспечивать возможность подтверждения факта уведомления</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K48"/>
+  <autoFilter ref="A1:K57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SOUT_podpisanty_skvoznaya.xlsx
@@ -2,24 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$K$68</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +28,38 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <strike val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <strike val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,16 +68,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -69,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -77,9 +119,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -442,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -515,3088 +567,3693 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="114.75" customHeight="1">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ; Приказ Минтруда России от 29.10.2021 № 776н</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>ст. 214, ст. 217 ТК РФ; п. 1 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Положение о системе управления охраной труда</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Политика и цели в области охраны труда; структура и порядок функционирования системы управления охраной труда; процедуры (процессы) СУОТ, включая специальную оценку условий труда как базовый процесс; распределение обязанностей, ответственности и полномочий в области охраны труда; порядок планирования, контроля и улучшения функционирования СУОТ (с учетом Примерного положения, утвержденного приказом Минтруда России № 776н)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>ст. 214 ТК РФ (разработка и утверждение локальных нормативных актов по охране труда с учетом мнения); ст. 372 ТК РФ</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Мотивированное мнение выборного органа первичной профсоюзной организации (иного представительного органа работников) при принятии Положения о системе управления охраной труда</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Мотивированное мнение по проекту локального нормативного акта (Положения о СУОТ) в порядке ст. 372 ТК РФ</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Выборный орган первичной профсоюзной организации или иной представительный орган работников (при наличии)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="63.75" customHeight="1">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>ст. 214 ТК РФ</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Реестр (перечень) нормативных правовых актов, содержащих требования охраны труда</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Перечень нормативных правовых актов (в том числе с использованием ЭВМ и баз данных), содержащих требования охраны труда, в соответствии со спецификой деятельности работодателя; обеспечение доступа работников к актуальным редакциям</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>ст. 223 ТК РФ</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Приказ (распоряжение) о создании службы охраны труда или о введении должности специалиста по охране труда</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Решение о создании службы охраны труда либо о введении должности специалиста по охране труда; структура службы и численность работников службы (при создании службы)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76.5" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>ст. 224 ТК РФ</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Положение о комитете (комиссии) по охране труда</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Цели, задачи и порядок работы комитета (комиссии) по охране труда; состав на паритетной основе; участие в проведении специальной оценки условий труда; участие в информировании работников о состоянии условий и охраны труда (с учетом Примерного положения о комитете (комиссии) по охране труда)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="63.75" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>ст. 224 ТК РФ</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Приказ (распоряжение) о создании комитета (комиссии) по охране труда</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Создание комитета (комиссии) по охране труда; состав представителей работодателя и представителей выборного органа первичной профсоюзной организации или иного уполномоченного представительного органа работников (при наличии)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="51" customFormat="1" customHeight="1" s="4">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>ст. 214.1 ТК РФ</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Приказ (распоряжение) о приостановлении работ на рабочих местах с опасным классом условий труда</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Приостановка работ на рабочих местах, условия труда на которых по результатам специальной оценки условий труда отнесены к опасному классу условий труда; срок (до устранения оснований опасного класса)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="89.25" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>ст. 214.1 ТК РФ</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>План мероприятий по устранению оснований, послуживших установлению опасного класса условий труда</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Мероприятия по устранению оснований, послуживших установлению опасного класса условий труда; разрабатывается работодателем с учетом мнения выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии); утверждается работодателем; копия направляется в территориальный орган Роструда</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="51" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>ст. 214.1 ТК РФ</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Мнение выборного органа первичной профсоюзной организации (иного представительного органа работников) при разработке плана мероприятий по устранению оснований опасного класса условий труда</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Мнение представительного органа работников, учитываемое при разработке плана мероприятий (ст. 214.1 ТК РФ)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Выборный орган первичной профсоюзной организации или иной представительный орган работников (при наличии)</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Охрана труда (раздел X ТК РФ)</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Трудовой кодекс Российской Федерации от 30.12.2001 № 197-ФЗ</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>ст. 216.2 ТК РФ</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Уведомление (информация) работника об отнесении условий труда на его рабочем месте к опасному классу условий труда</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Сведения об отнесении условий труда на рабочем месте работника по результатам специальной оценки условий труда к опасному классу условий труда; доводится работодателем незамедлительно</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="140.25" customHeight="1">
+      <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>п. 9–11 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Политика (стратегия) в области охраны труда</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Цели и мероприятия, направленные на сохранение жизни и здоровья работников; публичная декларация работодателя о намерении выполнять государственные нормативные требования охраны труда и добровольно принятые обязательства; обеспечение безопасных условий труда; управление рисками; устранение опасностей и снижение уровней профессиональных рисков; обязательство совершенствовать СУОТ; учет мнения представительного органа работников (при наличии). Может оформляться отдельным локальным актом либо разделом локального акта работодателя</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="63.75" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>п. 9, 10 (ж) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Мнение выборного органа первичной профсоюзной организации (иного уполномоченного работниками органа) при принятии Политики (стратегии) в области охраны труда</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Мнение представительного органа работников, учитываемое при принятии Политики (стратегии) в области охраны труда</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Выборный орган первичной профсоюзной организации или иной уполномоченный работниками представительный орган (при наличии)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="76.5" customHeight="1">
+      <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>п. 12–13, п. 55 (ж) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Приказ (распоряжение) о назначении лиц, ответственных за соблюдение требований охраны труда и обеспечение функционирования СУОТ</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Назначение работников, ответственных за соблюдение требований охраны труда; предоставление полномочий для взаимодействия в рамках функционирования СУОТ (включая организацию и контроль базового процесса специальной оценки условий труда); документирование информации об ответственных лицах и их полномочиях</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="89.25" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>п. 29–32, п. 48, п. 55 (а) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>План мероприятий по охране труда</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Наименование мероприятий; ожидаемый результат по каждому мероприятию; сроки реализации; ответственные лица; выделяемые ресурсы и источники финансирования. При составлении учитываются в том числе изменения условий труда по результатам специальной оценки условий труда (СОУТ) и оценки профессиональных рисков (ОПР)</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76.5" customHeight="1">
+      <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>п. 44–46, п. 55 (е) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Порядок (процедура) информирования работников и взаимодействия с работниками в рамках СУОТ</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Порядок информирования работников о политике и целях в области охраны труда, об опасностях и рисках, о мерах управления; формы доведения информации, включая ознакомление работника с результатами специальной оценки условий труда и оценки профессиональных рисков; порядок взаимодействия с работниками</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76.5" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>п. 60–63, п. 55 (в) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Порядок контроля и оценки результативности функционирования СУОТ</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Объекты, методы и критерии контроля; виды контроля, в том числе контроль выполнения процессов периодического характера, включая специальную оценку условий труда работников; порядок оценки соответствия условий и охраны труда требованиям и анализ показателей функционирования СУОТ</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="63.75" customHeight="1">
+      <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>п. 63 (б), 67–69 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Документы (информация) по результатам контроля функционирования СУОТ</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Результаты контроля, измерений, анализа и оценки показателей деятельности СУОТ, в том числе по контролю выполнения специальной оценки условий труда; информация фиксируется и сохраняется работодателем</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="63.75" customFormat="1" customHeight="1" s="4">
+      <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>п. 63 (б), 67–69 Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Документы (информация) по результатам контроля функционирования СУОТ</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Результаты контроля, измерений, анализа и оценки показателей деятельности СУОТ, в том числе по контролю выполнения специальной оценки условий труда; информация фиксируется и сохраняется работодателем</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Специалист по охране труда (уполномоченное лицо работодателя)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="89.25" customHeight="1">
+      <c r="A20" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 29.10.2021 № 776н «Об утверждении Примерного положения о системе управления охраной труда»</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>п. 70–73, п. 55 (г) Примерного положения о СУОТ (приказ № 776н)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Порядок формирования корректирующих действий по совершенствованию функционирования СУОТ</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Порядок разработки корректирующих действий по совершенствованию СУОТ на основе результатов выполнения мероприятий по охране труда, анализа по результатам контроля, расследований, предписаний, предложений работников; в том числе с учетом результатов специальной оценки условий труда как базового процесса СУОТ</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76.5" customHeight="1">
+      <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>ст. 9 ч. 1, 2 ФЗ-426</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Приказ (распоряжение) о создании комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Состав комиссии (нечётное число членов); порядок деятельности комиссии; председатель комиссии; представители работодателя (в том числе специалист по охране труда); представители выборного органа первичной профсоюзной организации или иного представительного органа работников (при наличии)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="51" customHeight="1">
+      <c r="A22" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>ст. 9 ч. 1 ФЗ-426</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>График проведения специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Сроки (этапы) проведения специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="63.75" customHeight="1">
+      <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="63.75" customHeight="1">
+      <c r="A24" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>ст. 9 ч. 5 ФЗ-426; п. 13 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Перечень рабочих мест, на которых будет проводиться специальная оценка условий труда; указание аналогичных рабочих мест</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="51" customHeight="1">
+      <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>ст. 8 ч. 2, 6 ФЗ-426</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="51" customHeight="1">
+      <c r="A26" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>ст. 8 ч. 2, 6 ФЗ-426</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Гражданско-правовой договор о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Условия проведения специальной оценки условий труда; права и обязанности сторон; обязательства работодателя по предоставлению сведений, документов и информации об условиях труда</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="63.75" customHeight="1">
+      <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>ст. 8 ч. 6 ФЗ-426; п. 3 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Уведомление о получении идентификационного номера предстоящей специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Идентификационный номер предстоящей специальной оценки условий труда, полученный в Федеральной государственной информационной системе учета результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Уполномоченное лицо организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>УКЭП</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="76.5" customHeight="1">
+      <c r="A28" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>ст. 10 ФЗ-426; п. 6, 10 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>Заключение эксперта по результатам идентификации потенциально вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Результаты идентификации потенциально вредных и (или) опасных производственных факторов; при несовпадении наименований факторов с классификатором — фиксация отсутствия на рабочем месте вредных и (или) опасных производственных факторов, предусмотренных классификатором</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="63.75" customHeight="1">
+      <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="63.75" customHeight="1">
+      <c r="A30" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>ст. 10 ч. 5, ст. 12 ч. 2 ФЗ-426; п. 11 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Протокол заседания комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Решения комиссии (в том числе по результатам идентификации и о проведении исследований (испытаний) и измерений); особое мнение членов комиссии, не согласных с принятым решением (при наличии)</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="102" customHeight="1">
+      <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="102" customHeight="1">
+      <c r="A32" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>ст. 12 ч. 2 ФЗ-426; п. 12 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Перечень вредных и (или) опасных производственных факторов, подлежащих исследованиям (испытаниям) и измерениям, формируемый исходя из государственных нормативных требований охраны труда, характеристик технологического процесса и производственного оборудования, материалов и сырья, результатов ранее проводившихся исследований (испытаний) и измерений, предложений работников</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="255" customHeight="1">
+      <c r="A33" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>ст. 12 ч. 6, ст. 13, ст. 15 ч. 1 п. 4 ФЗ-426; п. 20 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Протоколы проведения исследований (испытаний) и измерений идентифицированных вредных и (или) опасных производственных факторов</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>По п. 20 Методики (приложение № 1 к приказу № 817н) протокол оформляется в отношении каждого вредного и (или) опасного фактора и содержит: полное наименование организации, проводящей СОУТ, номер в реестре, сведения об аккредитации; уникальный номер протокола на каждой странице с номером страницы; наименование и адреса работодателя; структурное подразделение (при наличии); индивидуальный номер рабочего места, должность (профессия, специальность) работника; наименование фактора по классификатору; дату проведения; сведения о средствах измерений; наименования методик (методов) измерений и реквизиты утвердивших их НПА; реквизиты НПА, регламентирующих ПДК (ПДУ, нормативные уровни); место проведения (при необходимости — эскиз); нормативное и фактическое значение уровня фактора; заключение по фактическому уровню с указанием класса (подкласса) условий труда по фактору; фамилии, имена, отчества (при наличии) и должности лиц, проводивших исследования (испытания) и измерения</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>Эксперт и (или) иной работник организации, проводящей специальную оценку условий труда, проводивший исследования (испытания) и измерения</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="63.75" customHeight="1">
+      <c r="A34" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>ст. 12 ч. 7 ФЗ-426; п. 21 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>Заключение эксперта о возможности использования результатов производственного контроля</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Заключение о возможности использования результатов исследований (испытаний) и измерений, проведенных аккредитованной испытательной лабораторией (центром) при осуществлении производственного контроля за условиями труда; прилагается к протоколу</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="76.5" customHeight="1">
+      <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>ст. 14, ст. 15 ч. 1 п. 5 ФЗ-426; п. 106 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Протокол оценки эффективности средств индивидуальной защиты</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Результаты оценки эффективности применяемых работниками, занятыми на рабочих местах с вредными условиями труда, средств индивидуальной защиты, прошедших обязательную сертификацию, проводимой в целях снижения класса (подкласса) условий труда (при проведении такой оценки)</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="63.75" customHeight="1">
+      <c r="A36" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="63.75" customHeight="1">
+      <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>ст. 12 ч. 9–11, ст. 15 ч. 1 п. 6 ФЗ-426; п. 23 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>Протокол комиссии, содержащий решение о невозможности проведения исследований (испытаний) и измерений</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Обоснование решения комиссии о невозможности проведения исследований (испытаний) и измерений; является неотъемлемой частью отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="63.75" customHeight="1">
+      <c r="A38" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
         <is>
           <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="39" ht="63.75" customHeight="1">
+      <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1–3 ФЗ-426; приложения № 3 и № 4 к приказу № 817н; п. 107–108 Методики</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="40" ht="63.75" customHeight="1">
+      <c r="A40" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 1 ФЗ-426; п. 3 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Руководитель организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="41" ht="63.75" customHeight="1">
+      <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ФЗ-426; приложения № 3 и № 4 к приказу № 817н</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Отчет о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K41" s="6" t="inlineStr">
         <is>
           <t>Заверение печатью организации, проводящей специальную оценку условий труда (при наличии) (п. 3 Инструкции по заполнению формы отчета, приложение № 4 к приказу Минтруда России № 817н)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="42" ht="63.75" customHeight="1">
+      <c r="A42" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="63.75" customHeight="1">
+      <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="63.75" customHeight="1">
+      <c r="A44" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="63.75" customHeight="1">
+      <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 3, ст. 16 ч. 2 ФЗ-426; раздел III приложения № 3 к приказу № 817н; п. 5 Инструкции по заполнению формы отчета (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Карта специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>Работник</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="63.75" customHeight="1">
+      <c r="A46" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="63.75" customHeight="1">
+      <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="63.75" customHeight="1">
+      <c r="A48" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 7 ФЗ-426; раздел IV приложения № 3 к приказу № 817н; п. 6 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>Сводная ведомость результатов проведения специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="63.75" customHeight="1">
+      <c r="A49" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>Председатель комиссии по проведению специальной оценки условий труда (как правило, руководитель организации)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="63.75" customHeight="1">
+      <c r="A50" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="63.75" customHeight="1">
+      <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 8, ст. 16 ч. 3 ФЗ-426; раздел V приложения № 3 к приказу № 817н; п. 7 Инструкции (приложение № 4 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>Перечень рекомендуемых мероприятий по улучшению условий труда</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="63.75" customHeight="1">
+      <c r="A52" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 1 п. 9 ФЗ-426</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Заключения эксперта организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Заключения эксперта организации, проводящей специальную оценку условий труда, по результатам ее проведения</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей специальную оценку условий труда</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="51" customHeight="1">
+      <c r="A53" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>ст. 5 ч. 1 п. 4, ст. 15 ч. 1 п. 10 ФЗ-426; п. 110 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>Замечания и возражения работника относительно результатов специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Замечания и возражения работника относительно результатов специальной оценки условий труда, проведенной на его рабочем месте, в письменном виде</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>Работник</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="63.75" customHeight="1">
+      <c r="A54" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 21.11.2023 № 817н</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 2 ФЗ-426; п. 2 Инструкции (приложение № 4 к приказу № 817н); п. 11, 108 Методики</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>Мотивированное особое мнение члена комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Мотивированное (аргументированное) особое мнение члена комиссии в письменной форме; прилагается к отчету о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>Член комиссии по проведению специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="63.75" customHeight="1">
+      <c r="A55" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Руководитель юридического лица (работодатель)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>собственноручная или УКЭП</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="6" t="inlineStr">
         <is>
           <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+    <row r="56" ht="63.75" customHeight="1">
+      <c r="A56" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»; Приказ Минтруда России от 17.06.2021 № 406н</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>ст. 11 ФЗ-426; п. 22 Методики (приложение № 1 к приказу № 817н); форма и Порядок подачи декларации (приказ № 406н)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>Декларация соответствия условий труда государственным нормативным требованиям охраны труда</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>Индивидуальный предприниматель (работодатель)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>собственноручная или УКЭП</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="6" t="inlineStr">
         <is>
           <t>Место печати (М.П.); заверение печатью (при наличии) (форма декларации и Порядок подачи, приложения № 1 и № 2 к приказу Минтруда России № 406н)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="57" ht="51" customHeight="1">
+      <c r="A57" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>СОУТ</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Федеральный закон от 28.12.2013 № 426-ФЗ «О специальной оценке условий труда»</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>ст. 15 ч. 5.1 ФЗ-426; п. 109 Методики (приложение № 1 к приказу № 817н)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>Уведомление организации, проводившей специальную оценку условий труда, об утверждении отчета о проведении специальной оценки условий труда</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Сведения об утверждении отчета о проведении специальной оценки условий труда; способ уведомления должен обеспечивать возможность подтверждения факта уведомления</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>п. 37.5 Рекомендаций (приказ № 926) — документирование процедуры оценки уровня профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Положение (порядок, процедура) оценки профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Описание процедуры оценки уровней профессиональных рисков; выбранный метод (методы) оценки; критерии степени тяжести и вероятности наступления негативного события; этапы выявления опасностей, оценки рисков, разработки мер управления; порядок документирования результатов</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>п. 3, 4, 9 Рекомендаций (приказ № 926) — выбор конкретных методов оценки осуществляется работодателем самостоятельно</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Приказ (распоряжение) об утверждении метода (методов) оценки уровней профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение выбранного метода (методов) оценки уровней профессиональных рисков либо указание на применение собственного метода работодателя исходя из специфики деятельности</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Рекомендаций (приказ № 926)</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Гражданско-правовой договор с организацией (экспертом), привлекаемой для оценки уровней профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Условия проведения оценки уровней профессиональных рисков на договорной основе; права и обязанности сторон</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Рекомендаций (приказ № 926)</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Гражданско-правовой договор с организацией (экспертом), привлекаемой для оценки уровней профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Условия проведения оценки уровней профессиональных рисков на договорной основе; права и обязанности сторон</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Уполномоченное лицо организации (эксперта), привлекаемой для оценки профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>п. 7 Рекомендаций (приказ № 926)</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Перечень опасных работ, выполняемых работниками</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Перечень опасных работ с учетом особенностей производственной деятельности работодателя</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>п. 37.2, 37.5, 88 Рекомендаций (приказ № 926)</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Перечень (реестр) опасностей (рисков) с результатами оценки уровней профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Перечень (реестр) всех выявленных опасностей по видам работ, рабочим местам, профессиям или структурным подразделениям; для каждой опасности фиксируются: результаты оценки уровня профессионального риска; перечень мероприятий, запланированных для снижения уровней высоких и умеренных профессиональных рисков и недопущения их повышения; действующие предупредительные и защитные меры (фиксация мер контроля для низких/малозначимых рисков). Допускается оформление ранжированного перечня (реестра) рисков (п. 88 Рекомендаций)</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>п. 37.2, 37.5, 88 Рекомендаций (приказ № 926)</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Перечень (реестр) опасностей (рисков) с результатами оценки уровней профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Перечень (реестр) всех выявленных опасностей по видам работ, рабочим местам, профессиям или структурным подразделениям; для каждой опасности фиксируются: результаты оценки уровня профессионального риска; перечень мероприятий, запланированных для снижения уровней высоких и умеренных профессиональных рисков и недопущения их повышения; действующие предупредительные и защитные меры (фиксация мер контроля для низких/малозначимых рисков). Допускается оформление ранжированного перечня (реестра) рисков (п. 88 Рекомендаций)</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Специалист по охране труда (уполномоченное лицо работодателя)</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>п. 37.4, 37.5, 90 Рекомендаций (приказ № 926); приложение № 16 к Рекомендациям</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>План мероприятий по управлению профессиональными рисками</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Мероприятия по устранению опасностей и снижению уровней профессиональных рисков с учетом приоритетности; для рисков, оцененных как умеренные, — план мероприятий по снижению; для высоких — срочные меры; для низких/малозначимых — фиксация действующих мер контроля. Рекомендуемая форма — приложение № 16 к Рекомендациям (приказ № 926) (не является обязательной унифицированной формой)</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>п. 91–93 Рекомендаций (приказ № 926)</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Результаты повторной оценки уровней профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Результаты повторной оценки уровней профессиональных рисков после реализации мероприятий по управлению профессиональными рисками; при сохранении высокого уровня — сведения о дополнительных мерах контроля и (или) применении СИЗ</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.12.2021 № 926 «Об утверждении Рекомендаций по выбору методов оценки уровней профессиональных рисков и по снижению уровней таких рисков»</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>п. 91–93 Рекомендаций (приказ № 926)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Результаты повторной оценки уровней профессиональных рисков</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Результаты повторной оценки уровней профессиональных рисков после реализации мероприятий по управлению профессиональными рисками; при сохранении высокого уровня — сведения о дополнительных мерах контроля и (или) применении СИЗ</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Специалист по охране труда (уполномоченное лицо работодателя)</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>ОПР (приказы № 926, № 771н)</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 29.10.2021 № 771н «Об утверждении Примерного перечня ежегодно реализуемых работодателем мероприятий по улучшению условий и охраны труда, ликвидации или снижению уровней профессиональных рисков либо недопущению повышения их уровней»; ст. 225 ТК РФ</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>ст. 225 ТК РФ; Примерный перечень (приложение к приказу № 771н), п. 1</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Перечень ежегодно реализуемых работодателем мероприятий по улучшению условий и охраны труда, ликвидации или снижению уровней профессиональных рисков либо недопущению повышения их уровней</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Перечень ежегодно реализуемых работодателем мероприятий по улучшению условий и охраны труда, ликвидации или снижению уровней профессиональных рисков либо недопущению повышения их уровней (формируется с учетом Примерного перечня, утвержденного приказом № 771н). Включает в том числе проведение специальной оценки условий труда, выявление и оценку опасностей, оценку уровней профессиональных рисков, реализацию мер, разработанных по результатам их проведения (п. 1 Примерного перечня)</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57"/>
+  <autoFilter ref="A1:K68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>